--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -189,7 +189,7 @@
     <t>Structure of left radial artery (body structure)</t>
   </si>
   <si>
-    <t>24781000205105</t>
+    <t>1268741004</t>
   </si>
   <si>
     <t>Structure of left superficial temporal artery (body structure)</t>
@@ -261,7 +261,7 @@
     <t>Structure of right pulmonary artery (body structure)</t>
   </si>
   <si>
-    <t>24791000205107</t>
+    <t>1268742006</t>
   </si>
   <si>
     <t>Structure of right superficial temporal artery (body structure)</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
